--- a/course-design-2/outputs/tables/ch5/26_stage25_factor_revision.xlsx
+++ b/course-design-2/outputs/tables/ch5/26_stage25_factor_revision.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_汇总" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_中位数基线" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_分组预测误差" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_方法与口径说明" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_方法与统计范围说明" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/course-design-2/outputs/tables/ch5/26_stage25_factor_revision.xlsx
+++ b/course-design-2/outputs/tables/ch5/26_stage25_factor_revision.xlsx
@@ -5591,8 +5591,6 @@
           <t>y_pred ≡ 192.532876（train 的 mean（均值）），validation / test 信息未参与估计</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5627,8 +5625,6 @@
           <t>y_pred ≡ 192.532876（train 的 mean（均值）），validation / test 信息未参与估计</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5663,8 +5659,6 @@
           <t>y_pred ≡ 175.000000（train 的 median（中位数）），validation / test 信息未参与估计</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5699,8 +5693,6 @@
           <t>y_pred ≡ 175.000000（train 的 median（中位数）），validation / test 信息未参与估计</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5735,8 +5727,6 @@
           <t>差值为 median 基线指标 − mean 基线指标；MAE 为负表示中位数基线误差更小，RMSE / R² 为正表示中位数基线的平方误差 / 解释度表现更差</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5771,8 +5761,6 @@
           <t>差值为 median 基线指标 − mean 基线指标；MAE 为负表示中位数基线误差更小，RMSE / R² 为正表示中位数基线的平方误差 / 解释度表现更差</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5780,12 +5768,6 @@
           <t>复现核对</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>30_model_comparison.xlsx / 03_Baseline（只读）</t>
@@ -5808,12 +5790,6 @@
           <t>复现核对</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>差值 {'validation_MAE': 0.0, 'validation_RMSE': 0.0, 'validation_R2': 0.0}；能否复现：True</t>
@@ -5836,12 +5812,6 @@
           <t>复现核对</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>用于完整性核对</t>
@@ -5864,12 +5834,6 @@
           <t>复现核对</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>与既有 test 对照值一致</t>
@@ -5892,12 +5856,6 @@
           <t>主模型选择核对</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>在非 Dummy 模型中按 validation MAE 最小者选主模型（scripts/14_train_salary_model.py: non_dummy.iloc[0]）</t>
@@ -5920,12 +5878,6 @@
           <t>主模型选择核对</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>median 基线低于 mean 基线（MAE 的常数最优解即中位数），但仍远高于主模型</t>
@@ -5946,12 +5898,6 @@
           <t>主模型选择核对</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>新增 median 常数基线不改变主模型选择：选择规则在非 Dummy 模型中进行，LightGBM 仍为 validation MAE 最低者（36.088217）；median 基线 validation MAE 为 61.733647，二者不在同一比较集合内。</t>
@@ -6062,7 +6008,6 @@
           <t>模型 FINAL（LightGBM）对测试集的一次性预测（既有产物，只读）</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6097,7 +6042,6 @@
           <t>薪资三分位边界（测试集 y_true 分位点）= 33.3% → 150.0 / 66.7% → 200.0 元/天；区间为左开右闭；薪资三分位各档样本数按该规则统计（并列值可能使各档不完全相等）</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6132,7 +6076,6 @@
           <t>薪资三分位边界（测试集 y_true 分位点）= 33.3% → 150.0 / 66.7% → 200.0 元/天；区间为左开右闭；薪资三分位各档样本数按该规则统计（并列值可能使各档不完全相等）</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6167,7 +6110,6 @@
           <t>薪资三分位边界（测试集 y_true 分位点）= 33.3% → 150.0 / 66.7% → 200.0 元/天；区间为左开右闭；薪资三分位各档样本数按该规则统计（并列值可能使各档不完全相等）</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6202,7 +6144,6 @@
           <t>薪资四分位边界（测试集 y_true 分位点）= 25.0% → 135.0 / 50.0% → 175.0 / 75.0% → 225.0 元/天；区间为左开右闭；薪资四分位各档样本数按该规则统计（并列值可能使各档不完全相等）</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6237,7 +6178,6 @@
           <t>薪资四分位边界（测试集 y_true 分位点）= 25.0% → 135.0 / 50.0% → 175.0 / 75.0% → 225.0 元/天；区间为左开右闭；薪资四分位各档样本数按该规则统计（并列值可能使各档不完全相等）</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6272,7 +6212,6 @@
           <t>薪资四分位边界（测试集 y_true 分位点）= 25.0% → 135.0 / 50.0% → 175.0 / 75.0% → 225.0 元/天；区间为左开右闭；薪资四分位各档样本数按该规则统计（并列值可能使各档不完全相等）</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6307,7 +6246,6 @@
           <t>薪资四分位边界（测试集 y_true 分位点）= 25.0% → 135.0 / 50.0% → 175.0 / 75.0% → 225.0 元/天；区间为左开右闭；薪资四分位各档样本数按该规则统计（并列值可能使各档不完全相等）</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6810,7 +6748,6 @@
           <t>单值字段（1 岗位 1 取值）</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6845,7 +6782,6 @@
           <t>单值字段（1 岗位 1 取值）</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6880,7 +6816,6 @@
           <t>单值字段（1 岗位 1 取值）</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6915,7 +6850,6 @@
           <t>单值字段（1 岗位 1 取值）</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6950,7 +6884,6 @@
           <t>单值字段（1 岗位 1 取值）</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6985,7 +6918,6 @@
           <t>单值字段（1 岗位 1 取值）</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -7020,7 +6952,6 @@
           <t>单值字段（1 岗位 1 取值）</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -7055,7 +6986,6 @@
           <t>单值字段（1 岗位 1 取值）</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -7090,7 +7020,6 @@
           <t>单值字段（1 岗位 1 取值）</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -7125,7 +7054,6 @@
           <t>单值字段（1 岗位 1 取值）</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -7160,7 +7088,6 @@
           <t>单值字段（1 岗位 1 取值）</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -7195,7 +7122,6 @@
           <t>单值字段（1 岗位 1 取值）</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -7230,7 +7156,6 @@
           <t>单值字段（1 岗位 1 取值）</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -7265,7 +7190,6 @@
           <t>单值字段（1 岗位 1 取值）</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -7300,7 +7224,6 @@
           <t>单值字段（1 岗位 1 取值）</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
